--- a/отчеты для СН/ПОКОМ ЗПФ/Луганск ПОКОМ ЗПФ.xlsx
+++ b/отчеты для СН/ПОКОМ ЗПФ/Луганск ПОКОМ ЗПФ.xlsx
@@ -1,29 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\отчеты для СН\ПОКОМ ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\отчеты для СН\ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557C3151-992A-478C-97EB-2F1B04639722}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC256022-C9E6-401A-84B9-47F19EA2C5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ЗПФ" sheetId="6" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -182,12 +174,12 @@
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -641,8 +633,8 @@
         <v>13</v>
       </c>
       <c r="H3" s="4">
-        <f>3*J3</f>
-        <v>4.5</v>
+        <f>4*J3</f>
+        <v>6</v>
       </c>
       <c r="J3">
         <v>1.5</v>
@@ -670,7 +662,7 @@
       </c>
       <c r="H4" s="4">
         <f>H3</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -695,7 +687,7 @@
       </c>
       <c r="H5" s="4">
         <f t="shared" ref="H5:H14" si="2">H4</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -722,7 +714,7 @@
       </c>
       <c r="H6" s="4">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -749,7 +741,7 @@
       </c>
       <c r="H7" s="4">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -776,7 +768,7 @@
       </c>
       <c r="H8" s="4">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -805,7 +797,7 @@
       </c>
       <c r="H9" s="4">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -832,7 +824,7 @@
       </c>
       <c r="H10" s="4">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -857,7 +849,7 @@
       </c>
       <c r="H11" s="4">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -882,7 +874,7 @@
       </c>
       <c r="H12" s="4">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -909,7 +901,7 @@
       </c>
       <c r="H13" s="4">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -936,7 +928,7 @@
       </c>
       <c r="H14" s="4">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.2">
